--- a/arquivos/AFDBR512021002936436585411000133REP_P_analisado.xlsx
+++ b/arquivos/AFDBR512021002936436585411000133REP_P_analisado.xlsx
@@ -21012,14 +21012,8 @@
           <t>22196c735021545f27b13ca6e9214617ba3f27b4e1783a76a9ce43122eb7ee83</t>
         </is>
       </c>
-      <c r="N218" t="b">
-        <v>0</v>
-      </c>
-      <c r="O218" t="inlineStr">
-        <is>
-          <t>144db57d8d308cf003401afda4b2b0abc6f0b7c8b06a889fae73d07873a085d5</t>
-        </is>
-      </c>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr"/>
       <c r="P218" t="n">
         <v>2</v>
       </c>
